--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484209_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484209_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.876099999999999</v>
+        <v>8.7926</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3592</v>
+        <v>6.5208</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5169</v>
+        <v>2.2718</v>
       </c>
       <c r="G2" t="n">
         <v>4.8383</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0416</v>
+        <v>0.9581</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3135</v>
+        <v>-0.1518</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3551</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>2.2149</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3001</v>
+        <v>3.0962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6287</v>
+        <v>1.3159</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6713</v>
+        <v>1.7803</v>
       </c>
       <c r="G3" t="n">
         <v>2.278</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2955</v>
+        <v>1.0916</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5226</v>
+        <v>0.1646</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8181</v>
+        <v>0.927</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6642</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1549</v>
+        <v>2.8516</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2811</v>
+        <v>0.7054</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8738</v>
+        <v>2.1462</v>
       </c>
       <c r="G4" t="n">
         <v>0.6994</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.498</v>
+        <v>0.1988</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9876</v>
+        <v>-0.5632</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4896</v>
+        <v>0.762</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0347</v>
+        <v>2.103</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2274</v>
+        <v>1.1868</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8072</v>
+        <v>0.9162</v>
       </c>
       <c r="G5" t="n">
         <v>1.2879</v>
@@ -844,13 +844,13 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.356</v>
+        <v>0.4244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3247</v>
+        <v>0.2841</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0313</v>
+        <v>0.1402</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0006</v>
+        <v>1.1077</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3252</v>
+        <v>1.4868</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3246</v>
+        <v>-0.3791</v>
       </c>
       <c r="G6" t="n">
         <v>0.3766</v>
@@ -922,13 +922,13 @@
         <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>0.624</v>
+        <v>0.7312</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1899</v>
+        <v>0.3516</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4341</v>
+        <v>0.3796</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5129</v>
+        <v>0.5673</v>
       </c>
       <c r="E7" t="n">
         <v>0.2162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2966</v>
+        <v>0.3511</v>
       </c>
       <c r="G7" t="n">
         <v>0.2812</v>
@@ -1000,13 +1000,13 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>0.1348</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8477</v>
+        <v>0.1015</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2285</v>
+        <v>-0.2384</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6191</v>
+        <v>0.34</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8181</v>
+        <v>1.6042</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1059</v>
+        <v>-1.1737</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.924</v>
+        <v>2.7779</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1849</v>
+        <v>2.708</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0642</v>
+        <v>0.0639</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2491</v>
+        <v>2.6441</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6332</v>
+        <v>-1.1038</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9583</v>
+        <v>-1.2377</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.1338</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7751</v>
+        <v>0.4973</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1517</v>
+        <v>-0.2935</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6234</v>
+        <v>0.7909</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9119</v>
+        <v>-2.2766</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0067</v>
+        <v>-1.6847</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0948</v>
+        <v>-0.5919</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6042</v>
+        <v>-3.8181</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1737</v>
+        <v>0.1059</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7779</v>
+        <v>-3.924</v>
       </c>
       <c r="J9" t="n">
-        <v>2.708</v>
+        <v>-2.1849</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0639</v>
+        <v>1.0642</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6441</v>
+        <v>-3.2491</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1038</v>
+        <v>-1.6332</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2377</v>
+        <v>-0.9583</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1338</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5161</v>
+        <v>1.3461</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0619</v>
+        <v>0.6955</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5457</v>
+        <v>0.6506</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5722</v>
+        <v>-2.7385</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1951</v>
+        <v>-4.0618</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6229</v>
+        <v>1.3233</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.7019</v>
+        <v>-2.103</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.3418</v>
+        <v>-3.3981</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.36</v>
+        <v>1.2951</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.7195</v>
+        <v>-1.1895</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8995</v>
+        <v>-1.8113</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.82</v>
+        <v>0.6218</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9824</v>
+        <v>-0.9135</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4423</v>
+        <v>-1.5868</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5401</v>
+        <v>0.6733</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6256</v>
+        <v>0.4547</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9467</v>
+        <v>-0.4613</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.916</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5545</v>
+        <v>1.4959</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2224</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1861</v>
+        <v>-3.4507</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8907</v>
+        <v>-3.8829</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7046</v>
+        <v>0.4323</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.103</v>
+        <v>-5.7019</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3981</v>
+        <v>-3.3418</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2951</v>
+        <v>-2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1895</v>
+        <v>-3.7195</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8113</v>
+        <v>-1.8995</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6218</v>
+        <v>-1.82</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9135</v>
+        <v>-1.9824</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5868</v>
+        <v>-1.4423</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6733</v>
+        <v>-0.5401</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0071</v>
+        <v>0.747</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2902</v>
+        <v>0.2588</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2973</v>
+        <v>0.4883</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4959</v>
+        <v>0.5545</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1407</v>
+        <v>-4.0257</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9954</v>
+        <v>-3.9349</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1453</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1578</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0171</v>
+        <v>0.1321</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2504</v>
+        <v>0.311</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2207</v>
+        <v>6.1284</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.278599999999998</v>
+        <v>-2.370799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>8.499099999999999</v>
+        <v>8.4994</v>
       </c>
       <c r="G13" t="n">
         <v>-4.4152</v>
@@ -1441,7 +1441,7 @@
         <v>3.373400000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5735</v>
+        <v>4.573499999999999</v>
       </c>
       <c r="K13" t="n">
         <v>1.1932</v>
@@ -1450,7 +1450,7 @@
         <v>3.380400000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.988600000000002</v>
+        <v>-8.9886</v>
       </c>
       <c r="N13" t="n">
         <v>-8.9816</v>
@@ -1459,7 +1459,7 @@
         <v>-0.007099999999999995</v>
       </c>
       <c r="P13" t="n">
-        <v>2.930099999999999</v>
+        <v>2.9301</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.7205</v>
@@ -1468,16 +1468,16 @@
         <v>14.6506</v>
       </c>
       <c r="S13" t="n">
-        <v>5.764200000000001</v>
+        <v>6.672099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1776000000000003</v>
+        <v>0.7306000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>5.9417</v>
+        <v>5.941700000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9414000000000001</v>
+        <v>0.9414</v>
       </c>
       <c r="W13" t="n">
         <v>4.0458</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1529</v>
+        <v>6.1446</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2449</v>
+        <v>3.7505</v>
       </c>
       <c r="F14" t="n">
-        <v>1.908</v>
+        <v>2.3942</v>
       </c>
       <c r="G14" t="n">
         <v>7.2328</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7312</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9972</v>
+        <v>-1.4917</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2661</v>
+        <v>0.7523</v>
       </c>
       <c r="V14" t="n">
         <v>0.4326</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7367</v>
+        <v>1.6781</v>
       </c>
       <c r="E15" t="n">
         <v>0.3041</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4326</v>
+        <v>1.374</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1857</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2097</v>
+        <v>-0.2683</v>
       </c>
       <c r="T15" t="n">
         <v>-1.2626</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0529</v>
+        <v>0.9943</v>
       </c>
       <c r="V15" t="n">
         <v>1.374</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7937</v>
+        <v>1.1631</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1555</v>
+        <v>-0.0544</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9492</v>
+        <v>1.2174</v>
       </c>
       <c r="G16" t="n">
         <v>1.0872</v>
@@ -1702,13 +1702,13 @@
         <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1364</v>
+        <v>-0.767</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2626</v>
+        <v>-1.1615</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1263</v>
+        <v>0.3945</v>
       </c>
       <c r="V16" t="n">
         <v>1.4288</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8527</v>
+        <v>-1.7049</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6396</v>
+        <v>-1.4374</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2131</v>
+        <v>-0.2675</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4819</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1754</v>
+        <v>-1.0276</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6657</v>
+        <v>-0.4635</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5641</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2681</v>
+        <v>-2.0372</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4574</v>
+        <v>-2.6596</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1893</v>
+        <v>0.6224</v>
       </c>
       <c r="G18" t="n">
         <v>-0.551</v>
@@ -1858,13 +1858,13 @@
         <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8072</v>
+        <v>-0.5764</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.96</v>
+        <v>-1.1622</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1528</v>
+        <v>0.5858</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SEKOU MOUSSA</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9743</v>
+        <v>-3.4632</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5477</v>
+        <v>-3.7425</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4266</v>
+        <v>0.2794</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0919</v>
+        <v>-0.5945</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4032</v>
+        <v>-1.0655</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6887</v>
+        <v>0.471</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2022</v>
+        <v>-0.299</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3236</v>
+        <v>-1.7153</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1214</v>
+        <v>1.4163</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8897</v>
+        <v>-0.2955</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0795</v>
+        <v>0.6498</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8101</v>
+        <v>-0.9453</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.5162</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0329</v>
+        <v>-0.3914</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5381</v>
+        <v>-0.8259</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5053</v>
+        <v>0.4345</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3991</v>
+        <v>-2.2819</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3991</v>
+        <v>-1.6177</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>T. SEKOU MOUSSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.809</v>
+        <v>-4.979</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2481</v>
+        <v>-4.66</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5608</v>
+        <v>-0.319</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5945</v>
+        <v>-1.0919</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0655</v>
+        <v>-0.4032</v>
       </c>
       <c r="I20" t="n">
-        <v>0.471</v>
+        <v>-0.6887</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.299</v>
+        <v>-0.2022</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7153</v>
+        <v>-0.3236</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4163</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2955</v>
+        <v>-0.8897</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6498</v>
+        <v>-0.0795</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9453</v>
+        <v>-0.8101</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-3.5162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7372</v>
+        <v>0.0282</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3315</v>
+        <v>0.4259</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4057</v>
+        <v>-0.3977</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2819</v>
+        <v>-0.3991</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6177</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2208</v>
+        <v>-3.198500000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.4993</v>
+        <v>-8.499300000000002</v>
       </c>
       <c r="F21" t="n">
-        <v>3.278600000000001</v>
+        <v>5.3009</v>
       </c>
       <c r="G21" t="n">
         <v>4.415</v>
@@ -2068,10 +2068,10 @@
         <v>8.988700000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>8.9818</v>
+        <v>8.981799999999998</v>
       </c>
       <c r="L21" t="n">
-        <v>0.006799999999999695</v>
+        <v>0.006799999999999737</v>
       </c>
       <c r="M21" t="n">
         <v>-4.5736</v>
@@ -2092,13 +2092,13 @@
         <v>11.7206</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.764200000000001</v>
+        <v>-3.7419</v>
       </c>
       <c r="T21" t="n">
-        <v>-5.9415</v>
+        <v>-5.941499999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1775</v>
+        <v>2.1996</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9414999999999996</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484209_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484209_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0962</v>
+        <v>3.3419</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3159</v>
+        <v>3.3419</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7803</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.278</v>
+        <v>3.3419</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0386</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2394</v>
+        <v>3.0349</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4331</v>
+        <v>3.3419</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8358</v>
+        <v>3.0349</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.155</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5587</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4037</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0916</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1646</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.927</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8516</v>
+        <v>3.0962</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7054</v>
+        <v>1.3159</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1462</v>
+        <v>1.7803</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6994</v>
+        <v>2.278</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8619</v>
+        <v>0.0386</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1625</v>
+        <v>2.2394</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2686</v>
+        <v>2.4331</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6999</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4313</v>
+        <v>1.8358</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5692</v>
+        <v>-0.155</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.838</v>
+        <v>-0.5587</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2688</v>
+        <v>0.4037</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1988</v>
+        <v>1.0916</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5632</v>
+        <v>0.1646</v>
       </c>
       <c r="U4" t="n">
-        <v>0.762</v>
+        <v>0.927</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +819,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.103</v>
+        <v>2.8516</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1868</v>
+        <v>0.7054</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9162</v>
+        <v>2.1462</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2879</v>
+        <v>0.6994</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2901</v>
+        <v>0.8619</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9978</v>
+        <v>-0.1625</v>
       </c>
       <c r="J5" t="n">
-        <v>1.098</v>
+        <v>1.2686</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3697</v>
+        <v>1.6999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7284</v>
+        <v>-0.4313</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1899</v>
+        <v>-0.5692</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0795</v>
+        <v>-0.838</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2694</v>
+        <v>0.2688</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4244</v>
+        <v>0.1988</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2841</v>
+        <v>-0.5632</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1402</v>
+        <v>0.762</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,12 +880,17 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1077</v>
+        <v>2.103</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4868</v>
+        <v>1.1868</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3791</v>
+        <v>0.9162</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3766</v>
+        <v>1.2879</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3748</v>
+        <v>0.2901</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9982</v>
+        <v>0.9978</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3306</v>
+        <v>1.098</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9238</v>
+        <v>0.3697</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.954</v>
+        <v>0.1899</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.549</v>
+        <v>-0.0795</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>0.2694</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7312</v>
+        <v>0.4244</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3516</v>
+        <v>0.2841</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3796</v>
+        <v>0.1402</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5673</v>
+        <v>1.1077</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2162</v>
+        <v>1.4868</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3511</v>
+        <v>-0.3791</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2812</v>
+        <v>0.3766</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2407</v>
+        <v>1.3748</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0405</v>
+        <v>-0.9982</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0814</v>
+        <v>1.3306</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>1.9238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1998</v>
+        <v>-0.954</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1998</v>
+        <v>-0.549</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.7312</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1348</v>
+        <v>0.3516</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.044</v>
+        <v>0.3796</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1068,72 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1015</v>
+        <v>0.5673</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2384</v>
+        <v>0.2162</v>
       </c>
       <c r="F8" t="n">
-        <v>0.34</v>
+        <v>0.3511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6042</v>
+        <v>0.2812</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1737</v>
+        <v>0.2407</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7779</v>
+        <v>0.0405</v>
       </c>
       <c r="J8" t="n">
-        <v>2.708</v>
+        <v>0.0814</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0639</v>
+        <v>0.0409</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6441</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1038</v>
+        <v>0.1998</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2377</v>
+        <v>0.1998</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1338</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4973</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2935</v>
+        <v>0.1348</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7909</v>
+        <v>-0.044</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4507</v>
+        <v>-3.2404</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8829</v>
+        <v>-3.5803</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4323</v>
+        <v>0.34</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.7019</v>
+        <v>-1.7377</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3418</v>
+        <v>-1.4807</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.36</v>
+        <v>-0.257</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7195</v>
+        <v>-0.6339</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8995</v>
+        <v>-0.243</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.82</v>
+        <v>-0.3908</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9824</v>
+        <v>-1.1038</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4423</v>
+        <v>-1.2377</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5401</v>
+        <v>0.1338</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
         <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>0.747</v>
+        <v>0.4973</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2588</v>
+        <v>-0.2935</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4883</v>
+        <v>0.7909</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2224</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0257</v>
+        <v>-3.4507</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9349</v>
+        <v>-3.8829</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.4323</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1578</v>
+        <v>-5.7019</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4073</v>
+        <v>-3.3418</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7505</v>
+        <v>-2.36</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2691</v>
+        <v>-3.7195</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6536</v>
+        <v>-1.8995</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6155</v>
+        <v>-1.82</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8887</v>
+        <v>-1.9824</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7536</v>
+        <v>-1.4423</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.135</v>
+        <v>-0.5401</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1321</v>
+        <v>0.747</v>
       </c>
       <c r="T12" t="n">
-        <v>0.311</v>
+        <v>0.2588</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1789</v>
+        <v>0.4883</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1284</v>
+        <v>-4.0257</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.370799999999999</v>
+        <v>-3.9349</v>
       </c>
       <c r="F13" t="n">
-        <v>8.4994</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.4152</v>
+        <v>-4.1578</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.7885</v>
+        <v>-1.4073</v>
       </c>
       <c r="I13" t="n">
-        <v>3.373400000000001</v>
+        <v>-2.7505</v>
       </c>
       <c r="J13" t="n">
-        <v>4.573499999999999</v>
+        <v>-3.2691</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1932</v>
+        <v>-0.6536</v>
       </c>
       <c r="L13" t="n">
-        <v>3.380400000000001</v>
+        <v>-2.6155</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.9886</v>
+        <v>-0.8887</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.9816</v>
+        <v>-0.7536</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.007099999999999995</v>
+        <v>-0.135</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.7205</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>14.6506</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>6.672099999999999</v>
+        <v>0.1321</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7306000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="U13" t="n">
-        <v>5.941700000000001</v>
+        <v>-0.1789</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0458</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1446</v>
+        <v>6.128399999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7505</v>
+        <v>-2.370799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3942</v>
+        <v>8.4994</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2328</v>
+        <v>-4.4152</v>
       </c>
       <c r="H14" t="n">
-        <v>2.634</v>
+        <v>-7.7885</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5989</v>
+        <v>3.373400000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>8.282</v>
+        <v>4.573499999999997</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2771</v>
+        <v>1.1933</v>
       </c>
       <c r="L14" t="n">
-        <v>5.0049</v>
+        <v>3.380400000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0491</v>
+        <v>-8.9886</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6431</v>
+        <v>-8.9816</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.406</v>
+        <v>-0.007100000000000106</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7814</v>
+        <v>2.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-11.7205</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>14.6506</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7393999999999999</v>
+        <v>6.6721</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4917</v>
+        <v>0.7306000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7523</v>
+        <v>5.9417</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4326</v>
+        <v>0.9414000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1097</v>
+        <v>4.0458</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5423</v>
-      </c>
+        <v>-3.1045</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6781</v>
+        <v>6.1446</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3041</v>
+        <v>3.7505</v>
       </c>
       <c r="F15" t="n">
-        <v>1.374</v>
+        <v>2.3942</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1857</v>
+        <v>7.2328</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3771</v>
+        <v>2.634</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5628</v>
+        <v>4.5989</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2064</v>
+        <v>8.282</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6807</v>
+        <v>3.2771</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.8871</v>
+        <v>5.0049</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-1.0491</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3036</v>
+        <v>-0.6431</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6757</v>
+        <v>-0.406</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2683</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2626</v>
+        <v>-1.4917</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9943</v>
+        <v>0.7523</v>
       </c>
       <c r="V15" t="n">
-        <v>1.374</v>
+        <v>0.4326</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>-0.1097</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3991</v>
+        <v>0.5423</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1631</v>
+        <v>1.6781</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0544</v>
+        <v>0.3041</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2174</v>
+        <v>1.374</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0872</v>
+        <v>-1.1857</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4232</v>
+        <v>1.3771</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.336</v>
+        <v>-2.5628</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9321</v>
+        <v>-0.2064</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4572</v>
+        <v>1.6807</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5251</v>
+        <v>-1.8871</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8449</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.034</v>
+        <v>-0.3036</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8109</v>
+        <v>-0.6757</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.767</v>
+        <v>-0.2683</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1615</v>
+        <v>-1.2626</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3945</v>
+        <v>0.9943</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4288</v>
+        <v>1.374</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1052</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6763</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7049</v>
+        <v>1.1631</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4374</v>
+        <v>-0.0544</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2675</v>
+        <v>1.2174</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4819</v>
+        <v>1.0872</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4602</v>
+        <v>2.4232</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9422</v>
+        <v>-1.336</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0029</v>
+        <v>1.9321</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9442</v>
+        <v>2.4572</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9414</v>
+        <v>-0.5251</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4848</v>
+        <v>-0.8449</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.484</v>
+        <v>-0.034</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0008</v>
+        <v>-0.8109</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0276</v>
+        <v>-0.767</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4635</v>
+        <v>-1.1615</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5641</v>
+        <v>0.3945</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4288</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6763</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0372</v>
+        <v>-1.7049</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6596</v>
+        <v>-1.4374</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6224</v>
+        <v>-0.2675</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.551</v>
+        <v>-0.4819</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3628</v>
+        <v>1.4602</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9137</v>
+        <v>-1.9422</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6615</v>
+        <v>1.9442</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1822</v>
+        <v>-1.9414</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0303</v>
+        <v>-0.4848</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2988</v>
+        <v>-0.484</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2685</v>
+        <v>-0.0008</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5764</v>
+        <v>-1.0276</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1622</v>
+        <v>-0.4635</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5858</v>
+        <v>-0.5641</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4632</v>
+        <v>-2.0372</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7425</v>
+        <v>-2.6596</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2794</v>
+        <v>0.6224</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5945</v>
+        <v>-0.551</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0655</v>
+        <v>1.3628</v>
       </c>
       <c r="I19" t="n">
-        <v>0.471</v>
+        <v>-1.9137</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.299</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7153</v>
+        <v>1.6615</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4163</v>
+        <v>-2.1822</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2955</v>
+        <v>-0.0303</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6498</v>
+        <v>-0.2988</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9453</v>
+        <v>0.2685</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3914</v>
+        <v>-0.5764</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8259</v>
+        <v>-1.1622</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4345</v>
+        <v>0.5858</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2819</v>
+        <v>-1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6177</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SEKOU MOUSSA</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.979</v>
+        <v>-3.4632</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.66</v>
+        <v>-3.7425</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.319</v>
+        <v>0.2794</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0919</v>
+        <v>-0.5945</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4032</v>
+        <v>-1.0655</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6887</v>
+        <v>0.471</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2022</v>
+        <v>-0.299</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3236</v>
+        <v>-1.7153</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>1.4163</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8897</v>
+        <v>-0.2955</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0795</v>
+        <v>0.6498</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8101</v>
+        <v>-0.9453</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.5162</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0282</v>
+        <v>-0.3914</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4259</v>
+        <v>-0.8259</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3977</v>
+        <v>0.4345</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3991</v>
+        <v>-2.2819</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3991</v>
+        <v>-1.6177</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. SEKOU MOUSSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,152 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-4.979</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.319</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.0919</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.4032</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.6887</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.2022</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.3236</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.8897</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.0795</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.8101</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.3977</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.3991</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.3991</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484209_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>-3.198500000000001</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>-8.499300000000002</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>5.3009</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>4.415</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>7.788600000000001</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>-3.373499999999999</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>8.988700000000001</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>8.981799999999998</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>0.006799999999999737</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>-4.5736</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>-1.1932</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>-3.3803</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>-14.6506</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>11.7206</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>-3.7419</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>-5.941499999999999</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>2.1996</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V22" t="n">
         <v>-0.9414999999999996</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W22" t="n">
         <v>3.1044</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>-4.0458</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
